--- a/tests/formats/mfn_excel/MFN_Roboter_only.xlsx
+++ b/tests/formats/mfn_excel/MFN_Roboter_only.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FZI\code\generalized-path-finding\tests\formats\mfn_excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\en986\Documents\Projects\Alltours\generalized_agv_path_finding\tests\formats\mfn_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1127C62-7539-49AB-BEDA-625C570CB3C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F35FCD83-2710-4636-ACE3-67A36B02660B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-8535" windowWidth="29040" windowHeight="17640" xr2:uid="{B8DE84FF-B3E8-4D87-8A95-BDBF8C6662ED}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{B8DE84FF-B3E8-4D87-8A95-BDBF8C6662ED}"/>
   </bookViews>
   <sheets>
     <sheet name="NetworkNodes" sheetId="3" r:id="rId1"/>
     <sheet name="NetworkPaths" sheetId="2" r:id="rId2"/>
     <sheet name="NetworkConnections" sheetId="1" r:id="rId3"/>
+    <sheet name="Fleets" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">NetworkConnections!$A$1:$K$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">NetworkNodes!$A$1:$W$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">NetworkPaths!$D$1:$M$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">NetworkConnections!$A$1:$K$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">NetworkNodes!$A$1:$W$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">NetworkPaths!$D$1:$M$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="62">
   <si>
     <t>N</t>
   </si>
@@ -40,12 +41,6 @@
     <t>Connection1</t>
   </si>
   <si>
-    <t>[String]</t>
-  </si>
-  <si>
-    <t>Freie Bemerkung, welche keinen Einfluss auf die Simulation hat.</t>
-  </si>
-  <si>
     <t>orientation</t>
   </si>
   <si>
@@ -187,12 +182,6 @@
     <t>X</t>
   </si>
   <si>
-    <t>Die angenommene Wegzeit für den Ebenenwechsel in Sekunden</t>
-  </si>
-  <si>
-    <t>[int]</t>
-  </si>
-  <si>
     <t>Aufzugsname</t>
   </si>
   <si>
@@ -202,67 +191,6 @@
     <t>Roboter</t>
   </si>
   <si>
-    <t>[double]</t>
-  </si>
-  <si>
-    <t>Id der Node</t>
-  </si>
-  <si>
-    <t>Pixel auf Bild der Ebene</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Id der </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>unidirektionalen</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Connection</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Id des </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>unidirektionalen</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Paths</t>
-    </r>
-  </si>
-  <si>
     <t>Path_1A</t>
   </si>
   <si>
@@ -285,13 +213,19 @@
   </si>
   <si>
     <t xml:space="preserve"> Roboter </t>
+  </si>
+  <si>
+    <t>fleet</t>
+  </si>
+  <si>
+    <t>avg_speed_mps</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -301,14 +235,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -354,22 +280,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -686,7 +607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD73832A-1FBC-4985-A5DF-25369F7E8B7C}">
-  <dimension ref="A1:W7"/>
+  <dimension ref="A1:W5"/>
   <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="17.6640625" customWidth="1"/>
@@ -694,328 +615,272 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B1" s="4" t="s">
+      <c r="A1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="F1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2">
+        <v>1.5</v>
+      </c>
+      <c r="C2">
+        <v>1.6</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>150</v>
+      </c>
+      <c r="F2">
+        <v>160</v>
+      </c>
+      <c r="G2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H2">
+        <v>0.01</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N2"/>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2">
+        <v>0.5</v>
+      </c>
+      <c r="R2" t="s">
         <v>27</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="S1" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="T1" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="U1" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="V1" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="W1" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:23" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
-      <c r="S2" s="2"/>
-      <c r="T2" s="2"/>
-      <c r="U2" s="2"/>
-      <c r="V2" s="2"/>
-      <c r="W2" s="2"/>
+      <c r="S2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T2"/>
+      <c r="U2"/>
+      <c r="V2"/>
+      <c r="W2"/>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="5" t="s">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="C3">
+        <v>2.4</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>229.99999999999997</v>
+      </c>
+      <c r="F3">
+        <v>240</v>
+      </c>
+      <c r="G3" t="s">
         <v>56</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
-      <c r="S3" s="5"/>
-      <c r="T3" s="5"/>
-      <c r="U3" s="5"/>
-      <c r="V3" s="5"/>
-      <c r="W3" s="5"/>
+      <c r="H3">
+        <v>0.01</v>
+      </c>
+      <c r="J3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q3">
+        <v>0.1</v>
+      </c>
+      <c r="R3" t="s">
+        <v>27</v>
+      </c>
+      <c r="S3" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B4">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="F4">
-        <v>160</v>
+        <v>240</v>
       </c>
       <c r="G4" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="H4">
         <v>0.01</v>
       </c>
       <c r="J4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="K4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M4" t="s">
         <v>28</v>
       </c>
-      <c r="M4" t="s">
-        <v>30</v>
-      </c>
       <c r="Q4">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="R4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="S4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B5">
-        <v>2.2999999999999998</v>
+        <v>1.5</v>
       </c>
       <c r="C5">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>229.99999999999997</v>
+        <v>150</v>
       </c>
       <c r="F5">
-        <v>240</v>
+        <v>160</v>
       </c>
       <c r="G5" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="H5">
         <v>0.01</v>
       </c>
       <c r="J5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="K5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5" t="s">
         <v>28</v>
-      </c>
-      <c r="M5" t="s">
-        <v>30</v>
       </c>
       <c r="Q5">
         <v>0.1</v>
       </c>
       <c r="R5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="S5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>2.4</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>300</v>
-      </c>
-      <c r="F6">
-        <v>240</v>
-      </c>
-      <c r="G6" t="s">
-        <v>65</v>
-      </c>
-      <c r="H6">
-        <v>0.01</v>
-      </c>
-      <c r="J6" t="s">
-        <v>31</v>
-      </c>
-      <c r="K6" t="s">
-        <v>31</v>
-      </c>
-      <c r="L6" t="s">
-        <v>28</v>
-      </c>
-      <c r="M6" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q6">
-        <v>0.1</v>
-      </c>
-      <c r="R6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7">
-        <v>1.5</v>
-      </c>
-      <c r="C7">
-        <v>1.6</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>150</v>
-      </c>
-      <c r="F7">
-        <v>160</v>
-      </c>
-      <c r="G7" t="s">
-        <v>66</v>
-      </c>
-      <c r="H7">
-        <v>0.01</v>
-      </c>
-      <c r="J7" t="s">
-        <v>31</v>
-      </c>
-      <c r="K7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L7" t="s">
-        <v>28</v>
-      </c>
-      <c r="M7" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q7">
-        <v>0.1</v>
-      </c>
-      <c r="R7" t="s">
-        <v>29</v>
-      </c>
-      <c r="S7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W3" xr:uid="{722C5049-67F5-4D34-BA8B-C96877DC8B4A}"/>
+  <autoFilter ref="A1:W1" xr:uid="{722C5049-67F5-4D34-BA8B-C96877DC8B4A}"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -1023,7 +888,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E622508-6A6C-469D-9F74-98CF2B9013FF}">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.88671875" bestFit="1" customWidth="1"/>
@@ -1033,202 +898,164 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" s="8" t="s">
+      <c r="A1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="C1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="E1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="F1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="7" t="s">
+      <c r="G1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="H1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="I1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="M1" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
+      <c r="J1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="J2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M2" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="J3" t="s">
+        <v>14</v>
+      </c>
+      <c r="M3" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4">
         <v>2</v>
       </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
       <c r="J4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
         <v>2</v>
       </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
+      <c r="H5">
+        <v>0.5</v>
       </c>
       <c r="J5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6">
-        <v>3</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-      <c r="J6" t="s">
-        <v>16</v>
-      </c>
-      <c r="M6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>64</v>
-      </c>
-      <c r="B7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E7">
-        <v>3</v>
-      </c>
-      <c r="F7">
-        <v>2</v>
-      </c>
-      <c r="H7">
-        <v>0.5</v>
-      </c>
-      <c r="J7" t="s">
-        <v>16</v>
-      </c>
-      <c r="M7" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="D1:M3" xr:uid="{F3B9DDB8-FB25-49C8-981E-1A013ECC792F}"/>
+  <autoFilter ref="D1:M1" xr:uid="{F3B9DDB8-FB25-49C8-981E-1A013ECC792F}"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -1236,7 +1063,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0BDF8D4-F853-400B-A69F-22F8FF9ECE1F}">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
@@ -1254,154 +1081,136 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="D2">
+        <v>90</v>
+      </c>
+      <c r="E2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G2" t="s">
+        <v>57</v>
+      </c>
+      <c r="I2" t="s">
+        <v>50</v>
+      </c>
+      <c r="J2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3">
+        <v>90</v>
+      </c>
+      <c r="E3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J3" t="s">
         <v>59</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4">
-        <v>90</v>
-      </c>
-      <c r="E4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G4" t="s">
-        <v>66</v>
-      </c>
-      <c r="I4" t="s">
-        <v>54</v>
-      </c>
-      <c r="J4" t="s">
-        <v>67</v>
-      </c>
-      <c r="K4" t="s">
+      <c r="K3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5">
-        <v>90</v>
-      </c>
-      <c r="E5" t="s">
-        <v>53</v>
-      </c>
-      <c r="F5" t="s">
-        <v>65</v>
-      </c>
-      <c r="G5" t="s">
-        <v>66</v>
-      </c>
-      <c r="I5" t="s">
-        <v>54</v>
-      </c>
-      <c r="J5" t="s">
-        <v>68</v>
-      </c>
-      <c r="K5" t="s">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K4" xr:uid="{4A1CA232-A6F5-407D-9A1D-FC8408101890}"/>
+  <autoFilter ref="A1:K2" xr:uid="{4A1CA232-A6F5-407D-9A1D-FC8408101890}"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F28137BC-7FA1-46D5-AD18-F771B256AA6F}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2">
+        <v>0.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/tests/formats/mfn_excel/MFN_Roboter_only.xlsx
+++ b/tests/formats/mfn_excel/MFN_Roboter_only.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\en986\Documents\Projects\Alltours\generalized_agv_path_finding\tests\formats\mfn_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F35FCD83-2710-4636-ACE3-67A36B02660B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{632DA370-C5E5-4DB8-BB4F-AB01BCC94BE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{B8DE84FF-B3E8-4D87-8A95-BDBF8C6662ED}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{B8DE84FF-B3E8-4D87-8A95-BDBF8C6662ED}"/>
   </bookViews>
   <sheets>
     <sheet name="NetworkNodes" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="63">
   <si>
     <t>N</t>
   </si>
@@ -219,6 +219,9 @@
   </si>
   <si>
     <t>avg_speed_mps</t>
+  </si>
+  <si>
+    <t>Connection2</t>
   </si>
 </sst>
 </file>
@@ -1152,7 +1155,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
@@ -1167,10 +1170,10 @@
         <v>49</v>
       </c>
       <c r="F3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G3" t="s">
         <v>56</v>
-      </c>
-      <c r="G3" t="s">
-        <v>57</v>
       </c>
       <c r="I3" t="s">
         <v>50</v>
